--- a/tame_output/ON/bt/strategyON_20240101.xlsx
+++ b/tame_output/ON/bt/strategyON_20240101.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-137.1%</t>
+          <t>-137.2%</t>
         </is>
       </c>
     </row>
@@ -43583,10 +43583,10 @@
         <v>3.114862060640172</v>
       </c>
       <c r="D1829" t="n">
-        <v>0.05267127127679128</v>
+        <v>0.05246151726149706</v>
       </c>
       <c r="E1829" t="n">
-        <v>3.135574144837142</v>
+        <v>3.135490243231025</v>
       </c>
       <c r="F1829" t="n">
         <v>1.693598838607934</v>

--- a/tame_output/ON/bt/strategyON_20240101.xlsx
+++ b/tame_output/ON/bt/strategyON_20240101.xlsx
@@ -43583,10 +43583,10 @@
         <v>3.114862060640172</v>
       </c>
       <c r="D1829" t="n">
-        <v>0.05246151726149706</v>
+        <v>0.05232287492395493</v>
       </c>
       <c r="E1829" t="n">
-        <v>3.135490243231025</v>
+        <v>3.135434786296007</v>
       </c>
       <c r="F1829" t="n">
         <v>1.693598838607934</v>

--- a/tame_output/ON/bt/strategyON_20240101.xlsx
+++ b/tame_output/ON/bt/strategyON_20240101.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>480.4%</t>
+          <t>479.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-137.2%</t>
+          <t>-142.8%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-31.1%</t>
         </is>
       </c>
     </row>
@@ -43583,10 +43583,10 @@
         <v>3.114862060640172</v>
       </c>
       <c r="D1829" t="n">
-        <v>0.05232287492395493</v>
+        <v>-0.003564321156602046</v>
       </c>
       <c r="E1829" t="n">
-        <v>3.135434786296007</v>
+        <v>3.113079907863785</v>
       </c>
       <c r="F1829" t="n">
         <v>1.693598838607934</v>

--- a/tame_output/ON/bt/strategyON_20240101.xlsx
+++ b/tame_output/ON/bt/strategyON_20240101.xlsx
@@ -43577,7 +43577,7 @@
         <v>45291</v>
       </c>
       <c r="B1829" t="n">
-        <v>3.172280865657719</v>
+        <v>3.17228086565772</v>
       </c>
       <c r="C1829" t="n">
         <v>3.114862060640172</v>
